--- a/AAII_Financials/Quarterly/KUBTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KUBTY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>KUBTY</t>
   </si>
@@ -656,168 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -854,86 +858,89 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>5143300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4422800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4492600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3936100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3813700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3895100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4143300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3812200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3638900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3681700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3792700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3872400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4184200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4502400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4489500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4619600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4587100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4256600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4341200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3896200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4345200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3827200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3997000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3591100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3678500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3417100</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -970,86 +977,89 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>3799400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3289000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3419400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2877300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2798300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2742600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2932600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2681900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2529900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2641800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2663900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2835200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2976800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3158700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3184200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3286900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3315900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3072800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3106800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2719000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6185900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5413500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>5557200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>5157100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2607600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2430500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1086,86 +1096,89 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>1343900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1133800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1073100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1058800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1015400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1152500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1210700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1130300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1109000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1040000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1128800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1037200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1207400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1343700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1305200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1332800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1271300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1183800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1234300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1177100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-1840600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-1586200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-1560200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-1566000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1070900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>986600</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1206,8 +1219,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1322,8 +1336,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1438,8 +1455,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1476,8 +1496,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1518,8 +1538,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1536,26 +1556,29 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1700</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN14" s="3">
         <v>-2300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1592,8 +1615,8 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1670,8 +1693,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1709,8 +1735,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1747,86 +1774,89 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>4899200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4032000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4142200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3492700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3586600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3434000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3630100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3261100</v>
-      </c>
-      <c r="W17" s="3">
-        <v>3306100</v>
       </c>
       <c r="X17" s="3">
         <v>3306100</v>
       </c>
       <c r="Y17" s="3">
+        <v>3306100</v>
+      </c>
+      <c r="Z17" s="3">
         <v>3355800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3604000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3861000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3994700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3957600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4111500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4201300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3817200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3820800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3497200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3886700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3383700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3234000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3316400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3041200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1863,86 +1893,89 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>244100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>390800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>350400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>443400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>227100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>461100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>513200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>551100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>332800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>375600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>436800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>268300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>323100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>507600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>531900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>508200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>385800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>439400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>520400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>399000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>458600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>443500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>541600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>357100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>362100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1983,8 +2016,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2021,86 +2055,89 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>18000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>24600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>53500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>27900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>47500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>18600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>20600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>13000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>22100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>12300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>25700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>26300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>22400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>32400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>45800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>34100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>125500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2137,86 +2174,89 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>434600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>540900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>518400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>620600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>383300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>593100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>652000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>679600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>472300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>555300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>596800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>419000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>491700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>662400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>698100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>663200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>533500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>566400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>657900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>518100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>587100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>584100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>683500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>488400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>595400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>500500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2253,8 +2293,8 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2295,8 +2335,8 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
@@ -2313,26 +2353,29 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>2000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2369,86 +2412,89 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>262100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>406800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>375000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>496900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>255100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>464200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>522500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>555300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>345700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>423100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>455400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>273400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>343800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>520600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>554000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>520500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>411600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>450200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>546700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>409400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>478300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>473400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>586200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>389200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>486100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>399600</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2485,86 +2531,89 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>73800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>111800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>71200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>131900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>64500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>126600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>120700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>151600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>90300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>109900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>106700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>71300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>83900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>131600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>139000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>137400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>78600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>118900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>140500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>114000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>230700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>124400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>192800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>111400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>120400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>108600</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2679,8 +2728,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2717,86 +2769,89 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>188300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>295100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>303800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>365000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>190600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>337500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>401800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>403700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>255400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>313200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>348700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>202100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>259900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>389000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>414900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>383100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>333000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>331300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>406200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>295300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>247600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>349000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>393300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>277900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>365700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>291000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2833,86 +2888,89 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>161800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>269000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>276100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>335800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>197000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>314900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>374200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>369000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>235000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>287400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>331100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>182900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>242500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>379100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>402200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>358300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>308400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>315800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>382300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>271500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>224500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>321400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>358800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>244300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>349600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>272700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3027,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3065,8 +3126,8 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -3107,8 +3168,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3125,8 +3186,8 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ29" s="3">
         <v>0</v>
@@ -3143,8 +3204,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3259,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3375,8 +3442,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3413,86 +3483,89 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>-18000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-24600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-53500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-27900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-47500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-18600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-20600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-26300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-32400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-45800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-34100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-125500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-24300</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3529,86 +3602,89 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>161800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>269000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>276100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>335800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>197000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>314900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>374200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>369000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>235000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>287400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>331100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>182900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>242500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>379100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>402200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>358300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>308400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>315800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>382300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>271500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>224500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>321400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>358800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>244300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>349600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>272700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3723,8 +3799,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3761,207 +3840,213 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>161800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>269000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>276100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>335800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>197000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>314900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>374200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>369000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>235000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>287400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>331100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>182900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>242500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>379100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>402200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>358300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>308400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>315800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>382300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>271500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>224500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>321400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>358800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>244300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>349600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>272700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4002,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4044,148 +4130,152 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1865800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1766500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1392200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1877200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1784000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1647300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1575700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1476400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1337300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1476400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1337300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1362300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1603200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1089700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1451300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2031300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1776800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1292600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1745900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1347800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1634000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1717400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2138100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1334400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1818900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2022200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2032600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2162900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2095100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2288800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1624400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4171400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1867300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1724400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1168800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1502700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1095400</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1017900</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>660200</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>588900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4199,71 +4289,71 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>507800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>392500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>540400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>361500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>349500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>407500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>306400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>350200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>366300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>542600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>742700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>664300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>655600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>565600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>667800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>543400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>513300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>428900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>390500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>508600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>465700</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4276,820 +4366,844 @@
       <c r="AN42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10930000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10982800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10817300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10744800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10918000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11148400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11005400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10459100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10284700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10459100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10284700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10636400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9164500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8114400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7842600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7246400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6792500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6739900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6922200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7218100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6738900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7146600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8274700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8681400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8953500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8869500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8839000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9667900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8798800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8546400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8177100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8306000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>16484100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7757900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7627200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>7742000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>7779000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>6845800</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4422900</v>
+      </c>
+      <c r="E44" s="3">
         <v>4393800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4656400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4403200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4464700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4675600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4739200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4699000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4746000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4699000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4746000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4869000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4575700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4266700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4261600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3842200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3504100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3344900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3151200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2928100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2741400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2796600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3145300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3419300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3483700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3661900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3590500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3755100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3499400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3565800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3480800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3430200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>6521200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3452500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3321500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3228200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3159300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2989900</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1610300</v>
+      </c>
+      <c r="E45" s="3">
         <v>483200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1635900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>553200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1257800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1319200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>396200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1139900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1043900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1139900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1043900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1194800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>392100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>637900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>569300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>586100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>406100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>525500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>458900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>439700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>530000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>504000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>442600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>692100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>747300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>652700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>530500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>489100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>502700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>464100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>449800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>442700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1502100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>937300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>896200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1001700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1423500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1366300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18829100</v>
+      </c>
+      <c r="E46" s="3">
         <v>18644200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18501800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18238500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18424500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18790500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18305400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17774400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17411900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17774400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17411900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18062500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16243200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14501200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14665300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14067500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12829100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12310500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12584500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12283800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12010500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12707200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14743500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14791500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15659000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15119300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15649900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16488100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15477100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15100300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14787100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14312000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14540200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>14015000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13569300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>13140700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>13864500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>12297400</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11716400</v>
+      </c>
+      <c r="E47" s="3">
         <v>1269800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11880300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1327500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11433300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11194700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1409400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11078400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11074800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11078400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11074800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11023700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10052100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9567800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1423900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1523300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1364000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1386300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1319700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1312300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1280600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1353500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1286300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1434600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1664100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1664000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1730400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1839500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1716300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1959100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1838400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1901000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2594100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>668400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>638600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>588700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>599700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>615400</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5753200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5997800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5888600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5481700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5016200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5076400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5157900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4680200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4733600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4680200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4733600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4937800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4574100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3933100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3915400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3483200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3409700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3310300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3237700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3084100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3112800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3096600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3352100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3473200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3692700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3496200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3464700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3670500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3115500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3009000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2865600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2860500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5930000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2885500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2822000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2757300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2787200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2563600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2152500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2094700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2279600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2096900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2276000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2299000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2219800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2320900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2384800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2320900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2384800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2439400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2264100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1850600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1731400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>716200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1317400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>596500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>590400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>548300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>531700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>533200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>552700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>547000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>555600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>507500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>489100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>503400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>471500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>442000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>425600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>418400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>856900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>409700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>397800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>391100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>408500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>373900</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5204,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5320,32 +5437,35 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>455700</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>267800</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>275100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5358,86 +5478,89 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>698300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>643300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8958100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7882100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7663500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7574300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7484000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6768600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6442000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6554000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6746300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6497900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7027800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6769600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6460300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6696700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6554600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6434600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5910100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5489100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>12878600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6833200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>6624300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>6173200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>6028200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5270300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5552,124 +5675,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39094100</v>
+      </c>
+      <c r="E54" s="3">
         <v>39575200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39268800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38281800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37800500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38035100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38019100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36409400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36111900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36409400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36111900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36986900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33831900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30495900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30694100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27672300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25925000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25177900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>25216300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23997100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23377700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24244500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26680900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>26744200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28599200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27556700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27794300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29198100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27335000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26945100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25826800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>24981000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25604600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>24811800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>24052000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>23051000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>23688100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>21120600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5710,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5752,704 +5882,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1631000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1890300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1773400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1747500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1904800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2086500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2134600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2187500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2043900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2187500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2043900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2619000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3228900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2465500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2651200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2513700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2695300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2372400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2415300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2249600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2372000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1967400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2087100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2203200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2676300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2599200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2952700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3138600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2895800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2766100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2721300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2691200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5173100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2491900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2228000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2123000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2269500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1897900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6186700</v>
+      </c>
+      <c r="E58" s="3">
         <v>5644700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4957100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5893800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5023500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5154500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4858600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4204100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4069200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4204100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4069200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5515500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9100600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4425400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4283700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4563400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3464800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2875100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3216100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3288500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2683100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2888400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3109900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3598600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3521400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3007500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2950600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3732200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3295100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3188900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2986200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3357000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>6577900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2849500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2942500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3099900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3007800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2710500</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3870800</v>
+      </c>
+      <c r="E59" s="3">
         <v>3760000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3856900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3650900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3709500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3796400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3598700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3499900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3500700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3499900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3500700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3881000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3464100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3122700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3099800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2846300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2865300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2709000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2608700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2583900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2468600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2483100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2783300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2801100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2928200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2800700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2678800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2866000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2520500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2415900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2432100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2254500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4851200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2258700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2173300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2080400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2143500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1891000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11688400</v>
+      </c>
+      <c r="E60" s="3">
         <v>11295000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10587500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11292200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10637800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11037300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10591900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9891500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9613800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9891500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9613800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12015500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11243400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10013500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10034600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9923400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9025400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7956500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8240100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8122100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7523700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7339000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7980300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8602900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9125900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8407400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8582100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9736700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8711400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8370900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8139600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8302800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8293800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7600100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7343800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7303300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7420800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6499400</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7697100</v>
+      </c>
+      <c r="E61" s="3">
         <v>9186900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9486000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9007600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9019000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9150000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9671600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9524000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9368500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9524000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9368500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7729300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6888500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6108200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5898500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4631000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4054500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4168500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3815400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3440300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3726600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4527400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5054300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4420000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4704800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4979400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5065700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4697500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4627500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4698000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4540900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3902300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4254300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4520900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4259300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4032700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4247800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3795000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>384900</v>
+      </c>
+      <c r="E62" s="3">
         <v>117000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>331200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>101100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>301500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>325900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>108000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>282500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>318000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>282500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>318000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>354800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>772300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>526700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>566800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>533800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>581400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>546800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>574800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>586300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>588700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>483000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>551200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>596200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>764500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>638300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>714600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>767600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>530500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>536900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>514100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>550700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1317400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>588700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>605400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>534700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>737500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>662100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6564,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6680,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6796,124 +6951,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20390100</v>
+      </c>
+      <c r="E66" s="3">
         <v>21250900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20881100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20855500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20485300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21008000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20879200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20177100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19813200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20177100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19813200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20568100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20523000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17963700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17823500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15880100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14396900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13414000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13380700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12899700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12558300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13067100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14384900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14409400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15454900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14844500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15148800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16072900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14686800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14414200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13935100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13545200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13933100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13439100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12899700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12554400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13055100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>11544300</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6954,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7070,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7186,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7302,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7418,124 +7589,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12994500</v>
+      </c>
+      <c r="E72" s="3">
         <v>12474700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13144600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11654700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11290600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11493100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12015200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10961500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11287500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10961500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11287500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11826700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10857700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9697700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10273000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9843400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9890300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10283600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10349800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9604500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9717900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10205800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11029700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10905300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11285700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11084000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10972300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11056100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10718100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10311000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9946700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9551100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>19038100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9472700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9325000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8769500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8701000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8404700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7650,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7766,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7882,124 +8065,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17193800</v>
+      </c>
+      <c r="E76" s="3">
         <v>16729500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16637800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15757000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15648200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15348500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15435200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14626800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14713700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14626800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14713700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14619400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13308900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12532200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12870600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11792200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11528100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11763900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11835600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11097300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10819400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11177500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12296000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12334800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13144200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12712200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12645500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13125200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12648200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12530900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11891700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11435800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11671500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11372600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11152200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10496600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10633000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9576300</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8114,129 +8303,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8273,86 +8468,89 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>161800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>269000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>276100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>335800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>197000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>314900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>374200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>369000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>235000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>287400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>331100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>182900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>242500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>379100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>402200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>358300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>308400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>315800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>382300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>271500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>224500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>321400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>358800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>244300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>349600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>272700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8393,124 +8591,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>186300</v>
+      </c>
+      <c r="E83" s="3">
         <v>186900</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>180800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>179100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>190800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>184300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>145200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>156600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>145200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>156600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>153300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>172500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>134000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>143500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>123600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>128200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>128900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>129500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>124400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>126600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>132200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>141400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>145600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>147900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>141800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>144100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>142700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>122000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>116200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>111200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>108800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>104300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>104600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>100000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>98700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>107900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>100300</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8625,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8741,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8857,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8973,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9089,124 +9303,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1081800</v>
+      </c>
+      <c r="E89" s="3">
         <v>747400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>831400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>836200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>681600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>130400</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>256100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>47900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>256100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>47900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-790200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>447000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-310100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>419500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-559500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>306800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>538400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-159200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>547800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>145400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>657000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-242300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>416200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-130000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>369500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>101200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>191200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>97700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>707600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-177000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>559400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>502900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>971700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-24000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>498500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>319900</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9247,124 +9467,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-190400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-246100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-207400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-286400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-268700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-307100</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-207900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-288700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-207900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-288700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-286400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-40759000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-48247000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46727000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-33918000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-40178000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28572000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-211200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-110400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-107900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-137700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-145500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>4800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-297700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-128900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-291200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-257800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-157900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-118800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-54700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-218800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-109200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-150800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-221900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-162400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-123100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9479,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9595,124 +9822,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-253000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-345500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-205200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-488300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-424700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-380400</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-254500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-350200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-254500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-350200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-354800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-357700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-264700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1029400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-490700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-270200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-308300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-197800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-130200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-127600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-90600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-174400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-185600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-235900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-373300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-214300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-182300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1045400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-52500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>49600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-127500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-172400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-727200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9753,8 +9986,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9771,17 +10005,17 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>186500</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>189600</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
@@ -9791,86 +10025,89 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-167500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-167400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-183000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-162800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-161000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-204300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-191900</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-213200</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-183200</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-190700</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-167800</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-176100</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-154400</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9985,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10101,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10217,352 +10460,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-468900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-111000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-656200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-145400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-74800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>389100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>165300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>331100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>165300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>331100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>795700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>350800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>276900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-47400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1306600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>477200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-80300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>10600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-542300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-238100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>256200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>54200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>197900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-457100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-23000</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>86600</v>
       </c>
       <c r="AE100" s="3">
         <v>86600</v>
       </c>
       <c r="AF100" s="3">
+        <v>86600</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-184700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-137400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-114200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-155300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-148100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-17200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E101" s="3">
         <v>39600</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>14900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>55900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>13100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-52900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>15000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>51000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>15000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>51000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>71300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-49500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>46700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>57500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>31400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-10200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>51000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>15000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>23600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>32800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-25900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>16200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-29600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>25300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-13400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>15700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>6100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>98500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>399200</v>
+      </c>
+      <c r="E102" s="3">
         <v>349700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-64500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>312000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>235200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>178800</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>181900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>84700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>181900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>84700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-336300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>390500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-284200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-610600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>314000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>545200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-420000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>348700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-232700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-235200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>846200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-424700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>461300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-659200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>84700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-169300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>34000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-244000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>664400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-472800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>218400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>142900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>533200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-333900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>407300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-474100</v>
       </c>
     </row>
